--- a/var/data/original_files/week 36-37 N.xlsx
+++ b/var/data/original_files/week 36-37 N.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L83"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,11 +488,6 @@
           <t>Full Link</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Coordinates</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -536,7 +531,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -544,7 +539,6 @@
           <t>https://leadership.ng/2-die-4-others-injured-in-borno-bomb-explosion/</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -564,12 +558,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t xml:space="preserve">Russia, Belarus </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Moscow</t>
+          <t>Moscow, Minsk</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -588,7 +582,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -596,32 +590,31 @@
           <t>https://kyivindependent.com/russian-led-csto-starts-drills-in-belarus-with-nuclear-planning-practice/</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Cooperation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical, Biological, Radiological, Nuclear, Explosive</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russian-led CSTO starts drills in Belarus ahead of Zapad exercises</t>
+          <t>TRENDS Signs Research Cooperation Agreement with the Weapons and Hazardous Substances Office</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Belarus </t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>AbuDhabi</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -640,40 +633,39 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://kyivindependent.com/russian-led-csto-starts-drills-in-belarus-with-nuclear-planning-practice/</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>https://trendsresearch.org/news/trends-signs-research-cooperation-agreement-with-the-weapons-and-hazardous-substances-office/</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cooperation</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TRENDS Signs Research Cooperation Agreement with the Weapons and Hazardous Substances Office</t>
+          <t>GCC urges Iran to resolve islands dispute, calls for role in nuclear talks</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Iran, Kuwait</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AbuDhabi</t>
+          <t>Tehran, Kuwait</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -692,44 +684,43 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://trendsresearch.org/news/trends-signs-research-cooperation-agreement-with-the-weapons-and-hazardous-substances-office/</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>https://www.iranintl.com/en/202509019044</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cooperation</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TRENDS Signs Research Cooperation Agreement with the Weapons and Hazardous Substances Office</t>
+          <t>Syria suspected of nuclear reactor after IAEA discovers uranium remnants</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AbuDhabi</t>
+          <t>Damascus</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -739,25 +730,24 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://trendsresearch.org/news/trends-signs-research-cooperation-agreement-with-the-weapons-and-hazardous-substances-office/</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>https://newsukraine.rbc.ua/news/syria-suspected-of-nuclear-reactor-after-1756774707.html</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cooperation</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -767,17 +757,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TRENDS Signs Research Cooperation Agreement with the Weapons and Hazardous Substances Office</t>
+          <t>Sudan denies chemical or radioactive contamination in Khartoum</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AbuDhabi</t>
+          <t>Khartoum</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -791,25 +781,24 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://trendsresearch.org/news/trends-signs-research-cooperation-agreement-with-the-weapons-and-hazardous-substances-office/</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>https://sudantribune.com/article304592/</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cooperation</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -819,21 +808,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TRENDS Signs Research Cooperation Agreement with the Weapons and Hazardous Substances Office</t>
+          <t>Construction intensifies at site linked to Israel’s suspected nuclear program, satellite photos show</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AbuDhabi</t>
+          <t>Dimona</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45901</v>
+        <v>45903</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -848,15 +837,14 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://trendsresearch.org/news/trends-signs-research-cooperation-agreement-with-the-weapons-and-hazardous-substances-office/</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>https://www.thehindu.com/news/international/construction-intensifies-at-site-linked-to-israels-suspected-nuclear-program-satellite-photos-show/article70006838.ece</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -866,26 +854,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TRENDS Signs Research Cooperation Agreement with the Weapons and Hazardous Substances Office</t>
+          <t>Serbia, South Korea’s KHNP to cooperate on nuclear energy, hydrogen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Serbia, South Korea</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AbuDhabi</t>
+          <t>Belgrade, Seoul</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -900,15 +888,14 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://trendsresearch.org/news/trends-signs-research-cooperation-agreement-with-the-weapons-and-hazardous-substances-office/</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>https://balkangreenenergynews.com/serbia-south-koreas-khnp-to-cooperate-on-nuclear-energy-hydrogen/</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -923,21 +910,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GCC urges Iran to resolve islands dispute, calls for role in nuclear talks</t>
+          <t>China values Iran's commitment not to develop nuclear weapons, Xi tells Pezeshkia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>China, Iran</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Beijing, Tehran</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -952,20 +939,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://www.iranintl.com/en/202509019044</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>https://www.aa.com.tr/en/asia-pacific/china-values-irans-commitment-not-to-develop-nuclear-weapons-xi-tells-pezeshkian/3676444</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -975,21 +961,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GCC urges Iran to resolve islands dispute, calls for role in nuclear talks</t>
+          <t>IAEA to Conduct Third Extensive Sampling of Marine Environment Near Fukushima Daiichi Since Start of ALPS Treated Water Discharge</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Fukushima</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1004,40 +990,39 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://www.iranintl.com/en/202509019044</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>https://www.iaea.org/newscenter/pressreleases/iaea-to-conduct-third-extensive-sampling-of-marine-environment-near-fukushima-daiichi-since-start-of-alps-treated-water-discharge</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Syria suspected of nuclear reactor after IAEA discovers uranium remnants</t>
+          <t>Argentina's Zika Outbreak Records 730 Cases in 2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Damascus</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -1047,53 +1032,52 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>730</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://newsukraine.rbc.ua/news/syria-suspected-of-nuclear-reactor-after-1756774707.html</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>https://www.vax-before-travel.com/2025/09/02/argentinas-zika-outbreak-records-730-cases-2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sudan denies chemical or radioactive contamination in Khartoum</t>
+          <t>Tomato brown rugose fruit virus is officially confirmed in Egypt</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Khartoum</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1108,44 +1092,43 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://sudantribune.com/article304592/</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>https://www.hortidaily.com/article/9761494/tomato-brown-rugose-fruit-virus-is-officially-confirmed-in-egypt/</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t xml:space="preserve">Chemical </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Construction intensifies at site linked to Israel’s suspected nuclear program, satellite photos show</t>
+          <t>CDRT completes joint exercise to deal with chemical disasters</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t xml:space="preserve">Bangladesh </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dimona</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45903</v>
+        <v>45902</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1160,20 +1143,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/international/construction-intensifies-at-site-linked-to-israels-suspected-nuclear-program-satellite-photos-show/article70006838.ece</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>https://www.bssnews.net/others/307942</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cooperation</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1183,21 +1165,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia, South Korea’s KHNP to cooperate on nuclear energy, hydrogen</t>
+          <t>Vietnam open to using small module nuclear reactors</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Belgrade</t>
+          <t>Hanoi</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45902</v>
+        <v>45904</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1212,20 +1194,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://balkangreenenergynews.com/serbia-south-koreas-khnp-to-cooperate-on-nuclear-energy-hydrogen/</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>https://english.alarabiya.net/News/world/2025/09/04/vietnam-open-to-using-small-module-nuclear-reactors</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cooperation</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1235,21 +1216,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia, South Korea’s KHNP to cooperate on nuclear energy, hydrogen</t>
+          <t>Zaporizhia prepares for potential restart</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45902</v>
+        <v>45903</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1264,15 +1245,14 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://balkangreenenergynews.com/serbia-south-koreas-khnp-to-cooperate-on-nuclear-energy-hydrogen/</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>https://www.neimagazine.com/news/zaporizhia-prepares-for-potential-restart/</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1287,21 +1267,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China values Iran's commitment not to develop nuclear weapons, Xi tells Pezeshkia</t>
+          <t>Ethiopia Gains IAEA Support for Nuclear Energy Initiatives</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45902</v>
+        <v>45903</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1316,15 +1296,14 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://www.aa.com.tr/en/asia-pacific/china-values-irans-commitment-not-to-develop-nuclear-weapons-xi-tells-pezeshkian/3676444</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>https://birrmetrics.com/ethiopia-gains-iaea-support-for-nuclear-energy-initiatives/</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1339,21 +1318,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China values Iran's commitment not to develop nuclear weapons, Xi tells Pezeshkia</t>
+          <t>Korea proposes 292.6 billion won budget for enhanced nuclear safety and monitoring</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45902</v>
+        <v>45904</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1368,44 +1347,43 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://www.aa.com.tr/en/asia-pacific/china-values-irans-commitment-not-to-develop-nuclear-weapons-xi-tells-pezeshkian/3676444</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>https://biz.chosun.com/en/en-science/2025/09/04/TN4A4JEQQVETHBTXDVI3FAC46E/</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IAEA to Conduct Third Extensive Sampling of Marine Environment Near Fukushima Daiichi Since Start of ALPS Treated Water Discharge</t>
+          <t>Feds seize record 300,000 kilos of meth precursor chemicals in Houston port bust</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fukushima</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45902</v>
+        <v>45903</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1415,20 +1393,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human, Environment</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/iaea-to-conduct-third-extensive-sampling-of-marine-environment-near-fukushima-daiichi-since-start-of-alps-treated-water-discharge</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>https://cw39.com/crime/live-officials-report-record-chemical-bust-involving-foreign-terrorists/</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1443,44 +1420,43 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina's Zika Outbreak Records 730 Cases in 2025</t>
+          <t>Nipah virus in humans and animals: Pseudovirus test for detection developed, first in India</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45902</v>
+        <v>45908</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>730</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Human, Animal</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://www.vax-before-travel.com/2025/09/02/argentinas-zika-outbreak-records-730-cases-2025</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>https://keralakaumudi.com/en/news/news.php?id=1605679&amp;u=</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1495,21 +1471,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tomato brown rugose fruit virus is officially confirmed in Egypt</t>
+          <t>South Korea designates Nipah Virus as Level 1 infectious disease</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45902</v>
+        <v>45908</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1524,44 +1500,43 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://www.hortidaily.com/article/9761494/tomato-brown-rugose-fruit-virus-is-officially-confirmed-in-egypt/</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>https://www.chosun.com/english/travel-food-en/2025/09/08/FDIAEB5KJZFEVMSYULTV4IMTZI/</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CDRT completes joint exercise to deal with chemical disasters</t>
+          <t>Confirmed—The United Kingdom will invest £1.3 million in a system that converts urine and feces into data to detect viruses before they spread</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bangladesh </t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45902</v>
+        <v>45907</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1571,49 +1546,48 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human, Environment</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://www.bssnews.net/others/307942</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+          <t>https://www.blanquivioletas.com/en/united-kingdom-invest-detect-viruses/</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical, Biological, Radiological, Nuclear, Explosive</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vietnam open to using small module nuclear reactors</t>
+          <t>Heathrow Airport live: Terminal evacuated and firefighters attend ‘possible hazardous materials incident’</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45904</v>
+        <v>45908</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1623,49 +1597,48 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://english.alarabiya.net/News/world/2025/09/04/vietnam-open-to-using-small-module-nuclear-reactors</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>https://www.independent.co.uk/travel/news-and-advice/heathrow-airport-evacuated-live-updates-emergency-b2822540.html</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Zaporizhia prepares for potential restart</t>
+          <t>Calgary Police Lay Charges after Shipment found to Contain Hazardous Materials</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45903</v>
+        <v>45908</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1675,20 +1648,19 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human, Environment</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://www.neimagazine.com/news/zaporizhia-prepares-for-potential-restart/</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>https://hazmatmag.com/2025/09/08/calgary-police-lay-charges-after-shipment-found-to-contain-hazardous-materials/</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1698,26 +1670,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ethiopia Gains IAEA Support for Nuclear Energy Initiatives</t>
+          <t>MOECC, MCIT launch Hazardous Materials Management project</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45903</v>
+        <v>45908</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1727,20 +1699,19 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Environment, Infrastructure</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://birrmetrics.com/ethiopia-gains-iaea-support-for-nuclear-energy-initiatives/</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>https://www.gulf-times.com/article/710298/qatar/moecc-mcit-launch-hazardous-materials-management-project</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1755,21 +1726,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Korea proposes 292.6 billion won budget for enhanced nuclear safety and monitoring</t>
+          <t>Led by Emirates Nuclear Energy Company, Barakah Nuclear Energy Plant completes first year of full-fleet operations</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>AbuDhabi</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45904</v>
+        <v>45908</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1779,49 +1750,48 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Environment, Infrastructure</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-science/2025/09/04/TN4A4JEQQVETHBTXDVI3FAC46E/</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
+          <t>https://www.mediaoffice.abudhabi/en/energy/led-by-emirates-nuclear-energy-company-barakah-nuclear-energy-plant-completes-first-year-of-full-fleet-operations/</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Feds seize record 300,000 kilos of meth precursor chemicals in Houston port bust</t>
+          <t>Iran will accept nuclear curbs if sanctions lifted, Araghchi says</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t xml:space="preserve">Iran </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t xml:space="preserve">Tehran </t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45903</v>
+        <v>45908</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1831,49 +1801,48 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://cw39.com/crime/live-officials-report-record-chemical-bust-involving-foreign-terrorists/</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
+          <t>https://www.thenationalnews.com/news/mena/2025/09/08/iran-will-accept-nuclear-curbs-if-sanctions-lifted-araghchi-says/</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Cooperation</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Feds seize record 300,000 kilos of meth precursor chemicals in Houston port bust</t>
+          <t>Iran taps Doha to broker nuclear talks, signals flexibility on uranium stocks</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran, Qatar</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Tehran, Doha</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45903</v>
+        <v>45909</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1883,45 +1852,44 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://cw39.com/crime/live-officials-report-record-chemical-bust-involving-foreign-terrorists/</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
+          <t>https://www.iranintl.com/en/202509080879</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nipah virus in humans and animals: Pseudovirus test for detection developed, first in India</t>
+          <t>Restoring IAEA Inspections in Iran Would Create “Promising Ground” for Wider Progress, Says Director General Grossi</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -1935,45 +1903,44 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://keralakaumudi.com/en/news/news.php?id=1605679&amp;u=</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
+          <t>https://www.iaea.org/newscenter/news/restoring-iaea-inspections-in-iran-would-create-promising-ground-for-wider-progress-says-director-general-grossi</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nipah virus in humans and animals: Pseudovirus test for detection developed, first in India</t>
+          <t>Kazakhstan to Expand Nuclear Energy, Accelerate High-Tech Industrial Projects</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -1987,45 +1954,44 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Animal</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://keralakaumudi.com/en/news/news.php?id=1605679&amp;u=</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
+          <t>https://astanatimes.com/2025/09/kazakhstan-to-expand-nuclear-energy-accelerate-high-tech-industrial-projects/</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South Korea designates Nipah Virus as Level 1 infectious disease</t>
+          <t>Israel claims intercepting 3 drones from Yemen as sirens blare near nuclear facility</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t xml:space="preserve">JERUSALEM </t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -2039,49 +2005,48 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/english/travel-food-en/2025/09/08/FDIAEB5KJZFEVMSYULTV4IMTZI/</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+          <t>https://www.aa.com.tr/en/middle-east/israel-claims-intercepting-3-drones-from-yemen-as-sirens-blare-near-nuclear-facility/3681542</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Confirmed—The United Kingdom will invest £1.3 million in a system that converts urine and feces into data to detect viruses before they spread</t>
+          <t>Zaporizhzhia Nuclear Plant in Peril as IAEA Finds Six Safety Pillars Compromised by Russia</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -2091,49 +2056,48 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.blanquivioletas.com/en/united-kingdom-invest-detect-viruses/</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
+          <t>https://united24media.com/latest-news/zaporizhzhia-nuclear-plant-in-peril-as-iaea-finds-six-safety-pillars-compromised-by-russia-11483</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Cooperation</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Confirmed—The United Kingdom will invest £1.3 million in a system that converts urine and feces into data to detect viruses before they spread</t>
+          <t>Iranian officials to discuss nuclear file in Cairo</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Iran, Egypt</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Tehran, Cairo</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2143,49 +2107,48 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.blanquivioletas.com/en/united-kingdom-invest-detect-viruses/</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
+          <t>https://www.intellinews.com/iranian-officials-to-discuss-nuclear-file-in-cairo-400022/</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t xml:space="preserve">Chemical </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Heathrow Airport live: Terminal evacuated and firefighters attend ‘possible hazardous materials incident’</t>
+          <t>Union Minister Pralhad Joshi to inaugurate new chemical laboratory at NTH Ghaziabad</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45908</v>
+        <v>45907</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -2195,45 +2158,44 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Human, Environment</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://www.independent.co.uk/travel/news-and-advice/heathrow-airport-evacuated-live-updates-emergency-b2822540.html</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
+          <t>https://ddnews.gov.in/en/union-minister-pralhad-joshi-to-inaugurate-new-chemical-laboratory-at-nth-ghaziabad/</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Heathrow Airport live: Terminal evacuated and firefighters attend ‘possible hazardous materials incident’</t>
+          <t>Qatar demonstrates impressive progress in chemical risk management, says int'l policy expert</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -2247,49 +2209,48 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://www.independent.co.uk/travel/news-and-advice/heathrow-airport-evacuated-live-updates-emergency-b2822540.html</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
+          <t>https://thepeninsulaqatar.com/article/08/09/2025/qatar-demonstrates-impressive-progress-in-chemical-risk-management-says-intl-policy-expert</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Heathrow Airport live: Terminal evacuated and firefighters attend ‘possible hazardous materials incident’</t>
+          <t>Soldiers conduct chemical detection and reconnaissance training</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t xml:space="preserve">China </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>London</t>
+          <t xml:space="preserve">Beijing </t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45908</v>
+        <v>45909</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -2299,49 +2260,48 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://www.independent.co.uk/travel/news-and-advice/heathrow-airport-evacuated-live-updates-emergency-b2822540.html</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
+          <t>https://en.people.cn/n3/2025/0909/c90000-20363678.html</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Heathrow Airport live: Terminal evacuated and firefighters attend ‘possible hazardous materials incident’</t>
+          <t>New robotics and health technology centre opens in Liverpool, Australia</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45908</v>
+        <v>45909</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -2351,45 +2311,44 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://www.independent.co.uk/travel/news-and-advice/heathrow-airport-evacuated-live-updates-emergency-b2822540.html</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
+          <t>https://healthcareasiamagazine.com/healthcare/news/new-robotics-and-health-technology-centre-opens-in-liverpool-australia</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Heathrow Airport live: Terminal evacuated and firefighters attend ‘possible hazardous materials incident’</t>
+          <t>Infrastructure Challenges Hamper Latest Ebola Outbreak in DRC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Democratic Republic of Congo</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Kinshasa</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
@@ -2408,44 +2367,43 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://www.independent.co.uk/travel/news-and-advice/heathrow-airport-evacuated-live-updates-emergency-b2822540.html</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
+          <t>https://healthpolicy-watch.news/death-toll-climbs-in-latest-ebola-outbreak-in-drc/</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Calgary Police Lay Charges after Shipment found to Contain Hazardous Materials</t>
+          <t>Spain issues serious virus alert for 41 towns - full list of affected areas</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45908</v>
+        <v>45909</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -2460,40 +2418,39 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://hazmatmag.com/2025/09/08/calgary-police-lay-charges-after-shipment-found-to-contain-hazardous-materials/</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
+          <t>https://www.glasgowlive.co.uk/news/spain-issues-serious-virus-alert-32440122</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Calgary Police Lay Charges after Shipment found to Contain Hazardous Materials</t>
+          <t>Calls grow for Nigeria to fund health research as viral disease outbreaks spread</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Abuja</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -2507,49 +2464,48 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://hazmatmag.com/2025/09/08/calgary-police-lay-charges-after-shipment-found-to-contain-hazardous-materials/</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
+          <t>https://businessday.ng/news/article/calls-grow-for-nigeria-to-fund-health-research-as-viral-disease-outbreaks-spread/</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MOECC, MCIT launch Hazardous Materials Management project</t>
+          <t>Appili Therapeutics to Present Progress on Tularemia Biodefense Vaccine at NATO CBRN Conference</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Bern</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45908</v>
+        <v>45909</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2559,20 +2515,19 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Human, Weapon</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.gulf-times.com/article/710298/qatar/moecc-mcit-launch-hazardous-materials-management-project</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
+          <t>https://www.manilatimes.net/2025/09/09/tmt-newswire/globenewswire/appili-therapeutics-to-present-progress-on-tularemia-biodefense-vaccine-at-nato-cbrn-conference/2181361</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2582,26 +2537,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MOECC, MCIT launch Hazardous Materials Management project</t>
+          <t>Iran, UN nuclear watchdog progress on nuclear inspections</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Iran, Egypt</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Tehran, Cairo</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45908</v>
+        <v>45910</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -2616,15 +2571,14 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://www.gulf-times.com/article/710298/qatar/moecc-mcit-launch-hazardous-materials-management-project</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
+          <t>https://www.dw.com/en/iran-un-nuclear-watchdog-progress-on-nuclear-inspections/a-73941462</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2634,26 +2588,26 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Nuclear, Radiological</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Led by Emirates Nuclear Energy Company, Barakah Nuclear Energy Plant completes first year of full-fleet operations</t>
+          <t>Mitsubishi Heavy creates anti-radiation tents for nuclear accidents</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AbuDhabi</t>
+          <t>Niigata</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45908</v>
+        <v>45910</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -2663,25 +2617,24 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://www.mediaoffice.abudhabi/en/energy/led-by-emirates-nuclear-energy-company-barakah-nuclear-energy-plant-completes-first-year-of-full-fleet-operations/</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
+          <t>https://asia.nikkei.com/business/companies/mitsubishi-heavy-creates-anti-radiation-tents-for-nuclear-accidents</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2691,21 +2644,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Led by Emirates Nuclear Energy Company, Barakah Nuclear Energy Plant completes first year of full-fleet operations</t>
+          <t>IAEA-Led Team Conducts Marine Environmental Sampling Near Fukushima Daiichi Nuclear Power Station</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AbuDhabi</t>
+          <t>Okuma</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45908</v>
+        <v>45910</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2720,72 +2673,70 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://www.mediaoffice.abudhabi/en/energy/led-by-emirates-nuclear-energy-company-barakah-nuclear-energy-plant-completes-first-year-of-full-fleet-operations/</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
+          <t>https://www.iaea.org/newscenter/pressreleases/iaea-led-team-conducts-marine-environmental-sampling-near-fukushima-daiichi-nuclear-power-station</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Iran will accept nuclear curbs if sanctions lifted, Araghchi says</t>
+          <t>Four more H9N2 avian flu cases confirmed in China</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iran </t>
+          <t>China</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tehran </t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45908</v>
+        <v>45910</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://www.thenationalnews.com/news/mena/2025/09/08/iran-will-accept-nuclear-curbs-if-sanctions-lifted-araghchi-says/</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
+          <t>https://www.cidrap.umn.edu/avian-influenza-bird-flu/four-more-h9n2-avian-flu-cases-confirmed-china</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cooperation</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2795,21 +2746,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Iran taps Doha to broker nuclear talks, signals flexibility on uranium stocks</t>
+          <t>Tritium Level Far Below Japan’s Operational Limit in 15th Batch of ALPS-Treated Water, IAEA Confirms</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Okuma</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45909</v>
+        <v>45911</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2824,20 +2775,19 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.iranintl.com/en/202509080879</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+          <t>https://www.iaea.org/newscenter/pressreleases/tritium-level-far-below-japans-operational-limit-in-15th-batch-of-alps-treated-water-iaea-confirms</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cooperation</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2847,21 +2797,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Iran taps Doha to broker nuclear talks, signals flexibility on uranium stocks</t>
+          <t>Russia Says Ukraine Drones Hit Training Centre At Zaporizhzhia Nuclear Site</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Russia, Ukraine</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Moscow, Kyiv</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45909</v>
+        <v>45912</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2876,15 +2826,14 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://www.iranintl.com/en/202509080879</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
+          <t>https://www.ndtv.com/world-news/russia-says-ukraine-drones-hit-training-centre-at-zaporizhzhia-nuclear-plant-9261990</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2899,21 +2848,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Restoring IAEA Inspections in Iran Would Create “Promising Ground” for Wider Progress, Says Director General Grossi</t>
+          <t>IAEA: Morocco pledges to share its nuclear applications expertise with African countries</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Rabat</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45908</v>
+        <v>45911</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2928,15 +2877,14 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/news/restoring-iaea-inspections-in-iran-would-create-promising-ground-for-wider-progress-says-director-general-grossi</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
+          <t>https://northafricapost.com/90482-iaea-morocco-pledges-to-share-its-nuclear-applications-expertise-with-african-countries.html</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2946,26 +2894,26 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Radiological</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kazakhstan to Expand Nuclear Energy, Accelerate High-Tech Industrial Projects</t>
+          <t>A trace of radiation was found in the northern taiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Taiga</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45908</v>
+        <v>45912</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2975,49 +2923,48 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://astanatimes.com/2025/09/kazakhstan-to-expand-nuclear-energy-accelerate-high-tech-industrial-projects/</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
+          <t>https://www.oreanda-news.com/en/gosudarstvo/a-trace-of-radiation-was-found-in-the-northern-taiga/article1571949/</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Israel claims intercepting 3 drones from Yemen as sirens blare near nuclear facility</t>
+          <t>Gibraltar monitoring mosquitoes as West Nile Virus detected in nearby Spain</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Gibraltar</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">JERUSALEM </t>
+          <t>Gibraltar</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45908</v>
+        <v>45911</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -3027,49 +2974,48 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://www.aa.com.tr/en/middle-east/israel-claims-intercepting-3-drones-from-yemen-as-sirens-blare-near-nuclear-facility/3681542</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
+          <t>https://www.gbc.gi/news/gibraltar-monitoring-mosquitoes-as-west-nile-virus-detected-in-nearby-spain?fbclid=IwdGRjcAMwKExleHRuA2FlbQIxMQABHmlMsgqaW0PcULgaZ_VjQzFdfa3WaeYEFvy-SbuQdC5SjPZPc8-zJeH9PkcK_aem_nnQ8EawwZEwOaMFdO1zOWg</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Zaporizhzhia Nuclear Plant in Peril as IAEA Finds Six Safety Pillars Compromised by Russia</t>
+          <t>Bird flu outbreak shuts parks in Spain's Andalusia</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Andalusia</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45908</v>
+        <v>45911</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -3079,49 +3025,48 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Animal</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://united24media.com/latest-news/zaporizhzhia-nuclear-plant-in-peril-as-iaea-finds-six-safety-pillars-compromised-by-russia-11483</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
+          <t>https://www.france24.com/en/live-news/20250911-bird-flu-outbreak-shuts-parks-in-spain-s-andalusia</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cooperation</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical, Biological, Radiological, Nuclear, Explosive</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Iranian officials to discuss nuclear file in Cairo</t>
+          <t>Finland Hosts Major International Exercise on Hazardous Materials Emergency Response</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Helsinki</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45908</v>
+        <v>45911</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -3131,1632 +3076,70 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://www.intellinews.com/iranian-officials-to-discuss-nuclear-file-in-cairo-400022/</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
+          <t>https://suapress.com/archives/101009</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cooperation</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Iranian officials to discuss nuclear file in Cairo</t>
+          <t>Toxic Gas Leak in Tunisia’s Gafsa Causes Cases of Suffocation</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Moularès</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45908</v>
+        <v>45911</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human, Environment</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://www.intellinews.com/iranian-officials-to-discuss-nuclear-file-in-cairo-400022/</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Chemical</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Union Minister Pralhad Joshi to inaugurate new chemical laboratory at NTH Ghaziabad</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>45907</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>https://ddnews.gov.in/en/union-minister-pralhad-joshi-to-inaugurate-new-chemical-laboratory-at-nth-ghaziabad/</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Chemical</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Union Minister Pralhad Joshi to inaugurate new chemical laboratory at NTH Ghaziabad</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>45907</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Environment</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>https://ddnews.gov.in/en/union-minister-pralhad-joshi-to-inaugurate-new-chemical-laboratory-at-nth-ghaziabad/</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Chemical</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Qatar demonstrates impressive progress in chemical risk management, says int'l policy expert</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>45908</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>https://thepeninsulaqatar.com/article/08/09/2025/qatar-demonstrates-impressive-progress-in-chemical-risk-management-says-intl-policy-expert</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Chemical</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Soldiers conduct chemical detection and reconnaissance training</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">China </t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Beijing </t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>45909</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>https://en.people.cn/n3/2025/0909/c90000-20363678.html</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Biological</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>New robotics and health technology centre opens in Liverpool, Australia</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>45909</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>https://healthcareasiamagazine.com/healthcare/news/new-robotics-and-health-technology-centre-opens-in-liverpool-australia</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Biological</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Infrastructure Challenges Hamper Latest Ebola Outbreak in DRC</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Democratic Republic of Congo</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Kinshasa</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>45908</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>https://healthpolicy-watch.news/death-toll-climbs-in-latest-ebola-outbreak-in-drc/</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Biological</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Spain issues serious virus alert for 41 towns - full list of affected areas</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>45909</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>https://www.glasgowlive.co.uk/news/spain-issues-serious-virus-alert-32440122</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Biological</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Calls grow for Nigeria to fund health research as viral disease outbreaks spread</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Abuja</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>45908</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>https://businessday.ng/news/article/calls-grow-for-nigeria-to-fund-health-research-as-viral-disease-outbreaks-spread/</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Biological</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Appili Therapeutics to Present Progress on Tularemia Biodefense Vaccine at NATO CBRN Conference</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Bern</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>45909</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>https://www.manilatimes.net/2025/09/09/tmt-newswire/globenewswire/appili-therapeutics-to-present-progress-on-tularemia-biodefense-vaccine-at-nato-cbrn-conference/2181361</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Biological</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Appili Therapeutics to Present Progress on Tularemia Biodefense Vaccine at NATO CBRN Conference</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Bern</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>45909</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>https://www.manilatimes.net/2025/09/09/tmt-newswire/globenewswire/appili-therapeutics-to-present-progress-on-tularemia-biodefense-vaccine-at-nato-cbrn-conference/2181361</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Iran, UN nuclear watchdog progress on nuclear inspections</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Tehran</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>45910</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>https://www.dw.com/en/iran-un-nuclear-watchdog-progress-on-nuclear-inspections/a-73941462</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Iran, UN nuclear watchdog progress on nuclear inspections</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>45910</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>https://www.dw.com/en/iran-un-nuclear-watchdog-progress-on-nuclear-inspections/a-73941462</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Mitsubishi Heavy creates anti-radiation tents for nuclear accidents</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Niigata</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>45910</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>https://asia.nikkei.com/business/companies/mitsubishi-heavy-creates-anti-radiation-tents-for-nuclear-accidents</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Radiological</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Mitsubishi Heavy creates anti-radiation tents for nuclear accidents</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Niigata</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>45910</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>https://asia.nikkei.com/business/companies/mitsubishi-heavy-creates-anti-radiation-tents-for-nuclear-accidents</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>IAEA-Led Team Conducts Marine Environmental Sampling Near Fukushima Daiichi Nuclear Power Station</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Okuma</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>45910</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/iaea-led-team-conducts-marine-environmental-sampling-near-fukushima-daiichi-nuclear-power-station</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Biological</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Four more H9N2 avian flu cases confirmed in China</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>45910</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>4</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>https://www.cidrap.umn.edu/avian-influenza-bird-flu/four-more-h9n2-avian-flu-cases-confirmed-china</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Tritium Level Far Below Japan’s Operational Limit in 15th Batch of ALPS-Treated Water, IAEA Confirms</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Okuma</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/tritium-level-far-below-japans-operational-limit-in-15th-batch-of-alps-treated-water-iaea-confirms</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Incident</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Russia Says Ukraine Drones Hit Training Centre At Zaporizhzhia Nuclear Site</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Russia</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Moscow</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>45912</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>https://www.ndtv.com/world-news/russia-says-ukraine-drones-hit-training-centre-at-zaporizhzhia-nuclear-plant-9261990</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Incident</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Russia Says Ukraine Drones Hit Training Centre At Zaporizhzhia Nuclear Site</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Ukraine</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Kyiv</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="n">
-        <v>45912</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>https://www.ndtv.com/world-news/russia-says-ukraine-drones-hit-training-centre-at-zaporizhzhia-nuclear-plant-9261990</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>IAEA: Morocco pledges to share its nuclear applications expertise with African countries</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Rabat</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>https://northafricapost.com/90482-iaea-morocco-pledges-to-share-its-nuclear-applications-expertise-with-african-countries.html</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Radiological</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>A trace of radiation was found in the northern taiga</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Russia</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Taiga</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>45912</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Environmental</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>https://www.oreanda-news.com/en/gosudarstvo/a-trace-of-radiation-was-found-in-the-northern-taiga/article1571949/</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Biological</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Gibraltar monitoring mosquitoes as West Nile Virus detected in nearby Spain</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Gibraltar</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Gibraltar</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="G75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>https://www.gbc.gi/news/gibraltar-monitoring-mosquitoes-as-west-nile-virus-detected-in-nearby-spain?fbclid=IwdGRjcAMwKExleHRuA2FlbQIxMQABHmlMsgqaW0PcULgaZ_VjQzFdfa3WaeYEFvy-SbuQdC5SjPZPc8-zJeH9PkcK_aem_nnQ8EawwZEwOaMFdO1zOWg</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Biological</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Bird flu outbreak shuts parks in Spain's Andalusia</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Andalusia</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Animal</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>https://www.france24.com/en/live-news/20250911-bird-flu-outbreak-shuts-parks-in-spain-s-andalusia</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Chemical</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Finland Hosts Major International Exercise on Hazardous Materials Emergency Response</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Finland</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Helsinki</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Environmental</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>https://suapress.com/archives/101009</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Biological</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Finland Hosts Major International Exercise on Hazardous Materials Emergency Response</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Finland</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Helsinki</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Environmental</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>https://suapress.com/archives/101009</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Radiological</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Finland Hosts Major International Exercise on Hazardous Materials Emergency Response</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Finland</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Helsinki</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="G79" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Environmental</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>https://suapress.com/archives/101009</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Finland Hosts Major International Exercise on Hazardous Materials Emergency Response</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Finland</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Helsinki</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="G80" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Environmental</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>https://suapress.com/archives/101009</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Explosive</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Finland Hosts Major International Exercise on Hazardous Materials Emergency Response</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Finland</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Helsinki</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Environmental</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>https://suapress.com/archives/101009</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Incident</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Chemical</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Toxic Gas Leak in Tunisia’s Gafsa Causes Cases of Suffocation</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Moularès</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="G82" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" t="n">
-        <v>25</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
           <t>https://radioexpressfm.com/ar/%D8%A7%D9%84%D8%A3%D8%AE%D8%A8%D8%A7%D8%B1/%D8%AD%D8%A7%D9%84%D8%A7%D8%AA-%D8%A7%D8%AE%D8%AA%D9%86%D8%A7%D9%82-%D8%A8%D8%B3%D8%A8%D8%A8-%D8%A7%D9%86%D8%A8%D8%B9%D8%A7%D8%AB%D8%A7%D8%AA-%D8%BA%D8%A7%D8%B2%D9%8A%D8%A9-%D8%B3%D8%A7%D9%85%D8%A9/</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Incident</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Chemical</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Toxic Gas Leak in Tunisia’s Gafsa Causes Cases of Suffocation</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Moularès</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="G83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" t="n">
-        <v>25</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Environment</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>https://radioexpressfm.com/ar/%D8%A7%D9%84%D8%A3%D8%AE%D8%A8%D8%A7%D8%B1/%D8%AD%D8%A7%D9%84%D8%A7%D8%AA-%D8%A7%D8%AE%D8%AA%D9%86%D8%A7%D9%82-%D8%A8%D8%B3%D8%A8%D8%A8-%D8%A7%D9%86%D8%A8%D8%B9%D8%A7%D8%AB%D8%A7%D8%AA-%D8%BA%D8%A7%D8%B2%D9%8A%D8%A9-%D8%B3%D8%A7%D9%85%D8%A9/</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
